--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -144,10 +144,10 @@
     <t>An Nguyen</t>
   </si>
   <si>
-    <t>15/09/2025</t>
-  </si>
-  <si>
-    <t>09/10/2025</t>
+    <t>01-01-2025</t>
+  </si>
+  <si>
+    <t>01-01-2026</t>
   </si>
   <si>
     <t>Run auto test</t>
@@ -159,16 +159,16 @@
     <t>05-09-2026</t>
   </si>
   <si>
-    <t>20-09-2026</t>
+    <t>01-11-2026</t>
   </si>
   <si>
     <t>Lily Nguyen</t>
   </si>
   <si>
-    <t>05-09-2027</t>
-  </si>
-  <si>
-    <t>20-09-2027</t>
+    <t>05-10-2027</t>
+  </si>
+  <si>
+    <t>20-12-2027</t>
   </si>
 </sst>
 </file>
@@ -176,10 +176,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -211,7 +211,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,6 +240,59 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -241,48 +301,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -302,46 +323,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,181 +368,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,8 +559,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,8 +568,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -585,30 +585,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,164 +629,194 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1159,7 +1165,7 @@
       <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1167,17 +1173,17 @@
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1242,19 +1248,19 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I2" t="s">
@@ -1268,25 +1274,25 @@
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="I3" t="s">
@@ -1300,25 +1306,25 @@
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>34</v>
       </c>
       <c r="I4" t="s">
@@ -1378,10 +1384,10 @@
       <c r="C2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>43</v>
       </c>
       <c r="F2" t="s">
@@ -1395,13 +1401,13 @@
       <c r="B3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F3" t="s">
@@ -1415,13 +1421,13 @@
       <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="9" t="s">
         <v>50</v>
       </c>
       <c r="F4" t="s">

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13035" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12765" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
     <sheet name="Client" sheetId="1" r:id="rId2"/>
     <sheet name="Project" sheetId="3" r:id="rId3"/>
+    <sheet name="Task" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="95">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -123,6 +124,39 @@
     <t>lilynguyen</t>
   </si>
   <si>
+    <t>TC04</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>Tran</t>
+  </si>
+  <si>
+    <t>Long$2024</t>
+  </si>
+  <si>
+    <t>long.tran@test.com</t>
+  </si>
+  <si>
+    <t>longtran</t>
+  </si>
+  <si>
+    <t>TC05</t>
+  </si>
+  <si>
+    <t>Billy</t>
+  </si>
+  <si>
+    <t>Billy$2024</t>
+  </si>
+  <si>
+    <t>billy.billy@test.com</t>
+  </si>
+  <si>
+    <t>billy</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -138,7 +172,16 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>This is auto test</t>
+    <t>Endate_update</t>
+  </si>
+  <si>
+    <t>Status project</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>This is auto test1</t>
   </si>
   <si>
     <t>An Nguyen</t>
@@ -153,15 +196,39 @@
     <t>Run auto test</t>
   </si>
   <si>
+    <t>09-09-2026</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Highest</t>
+  </si>
+  <si>
+    <t>This is auto test2</t>
+  </si>
+  <si>
     <t>Alex Pham</t>
   </si>
   <si>
-    <t>05-09-2026</t>
+    <t>05-09-2025</t>
   </si>
   <si>
     <t>01-11-2026</t>
   </si>
   <si>
+    <t>09-09-2027</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>This is auto test3</t>
+  </si>
+  <si>
     <t>Lily Nguyen</t>
   </si>
   <si>
@@ -169,6 +236,72 @@
   </si>
   <si>
     <t>20-12-2027</t>
+  </si>
+  <si>
+    <t>09-09-2028</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>This is auto test4</t>
+  </si>
+  <si>
+    <t>Long Tran</t>
+  </si>
+  <si>
+    <t>05-10-2028</t>
+  </si>
+  <si>
+    <t>20-12-2028</t>
+  </si>
+  <si>
+    <t>09-09-2029</t>
+  </si>
+  <si>
+    <t>This is auto test5</t>
+  </si>
+  <si>
+    <t>Billy Billy</t>
+  </si>
+  <si>
+    <t>05-10-2029</t>
+  </si>
+  <si>
+    <t>20-12-2029</t>
+  </si>
+  <si>
+    <t>09-09-2030</t>
+  </si>
+  <si>
+    <t>TC06</t>
+  </si>
+  <si>
+    <t>This is auto test6</t>
+  </si>
+  <si>
+    <t>Tommy VN</t>
+  </si>
+  <si>
+    <t>05-10-2025</t>
+  </si>
+  <si>
+    <t>20-12-2030</t>
+  </si>
+  <si>
+    <t>09-09-2031</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Endate</t>
+  </si>
+  <si>
+    <t>Project</t>
   </si>
 </sst>
 </file>
@@ -176,10 +309,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -204,12 +337,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
@@ -218,14 +359,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,13 +380,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -254,8 +388,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,6 +443,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,52 +465,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -331,17 +473,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,187 +495,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -556,11 +689,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,17 +728,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,15 +772,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -656,15 +789,15 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -674,130 +807,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1196,8 +1329,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="4" max="4" width="12.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="11.6" customWidth="1"/>
@@ -1334,6 +1467,70 @@
         <v>24</v>
       </c>
     </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1343,95 +1540,305 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="12.5619047619048" customWidth="1"/>
-    <col min="2" max="2" width="14.8190476190476" customWidth="1"/>
+    <col min="2" max="2" width="16.0571428571429" customWidth="1"/>
     <col min="3" max="3" width="10.7809523809524" customWidth="1"/>
     <col min="4" max="4" width="10.8380952380952" customWidth="1"/>
     <col min="5" max="5" width="11.0952380952381" customWidth="1"/>
-    <col min="6" max="6" width="11.6380952380952" customWidth="1"/>
+    <col min="6" max="6" width="12.5047619047619" customWidth="1"/>
+    <col min="7" max="7" width="13.6952380952381" customWidth="1"/>
+    <col min="8" max="8" width="12.6190476190476" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.6857142857143" customWidth="1"/>
+    <col min="2" max="2" width="16.4857142857143" customWidth="1"/>
+    <col min="3" max="3" width="10.0666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>37</v>
+      <c r="B1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" t="s">
-        <v>44</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12765" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12765" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -181,6 +181,9 @@
     <t>Priority</t>
   </si>
   <si>
+    <t>Progress</t>
+  </si>
+  <si>
     <t>This is auto test1</t>
   </si>
   <si>
@@ -205,6 +208,9 @@
     <t>Highest</t>
   </si>
   <si>
+    <t>39</t>
+  </si>
+  <si>
     <t>This is auto test2</t>
   </si>
   <si>
@@ -226,6 +232,9 @@
     <t>Low</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>This is auto test3</t>
   </si>
   <si>
@@ -247,6 +256,9 @@
     <t>Normal</t>
   </si>
   <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>This is auto test4</t>
   </si>
   <si>
@@ -262,6 +274,9 @@
     <t>09-09-2029</t>
   </si>
   <si>
+    <t>68</t>
+  </si>
+  <si>
     <t>This is auto test5</t>
   </si>
   <si>
@@ -277,6 +292,9 @@
     <t>09-09-2030</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>TC06</t>
   </si>
   <si>
@@ -296,6 +314,9 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>Endate</t>
@@ -309,10 +330,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -344,7 +365,99 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,57 +471,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -419,66 +500,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -495,187 +516,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -686,6 +707,71 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -708,30 +794,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
@@ -745,59 +807,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -807,130 +828,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1540,7 +1561,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="12.5619047619048" customWidth="1"/>
@@ -1553,7 +1574,7 @@
     <col min="8" max="8" width="12.6190476190476" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1581,179 +1602,200 @@
       <c r="I1" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>62</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>70</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>78</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" t="s">
-        <v>74</v>
-      </c>
       <c r="I5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>70</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>62</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1784,10 +1826,10 @@
         <v>48</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>50</v>
@@ -1798,7 +1840,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1806,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1814,7 +1856,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1822,7 +1864,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1830,15 +1872,15 @@
         <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12765" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="13035" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="115">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -154,10 +154,10 @@
     <t>billy.billy@test.com</t>
   </si>
   <si>
-    <t>billy</t>
-  </si>
-  <si>
-    <t>Title</t>
+    <t>billy billy</t>
+  </si>
+  <si>
+    <t>Title project</t>
   </si>
   <si>
     <t>Client</t>
@@ -184,7 +184,13 @@
     <t>Progress</t>
   </si>
   <si>
-    <t>This is auto test1</t>
+    <t>Title file</t>
+  </si>
+  <si>
+    <t>Attach file</t>
+  </si>
+  <si>
+    <t>This is auto project1</t>
   </si>
   <si>
     <t>An Nguyen</t>
@@ -211,7 +217,10 @@
     <t>39</t>
   </si>
   <si>
-    <t>This is auto test2</t>
+    <t>Image test</t>
+  </si>
+  <si>
+    <t>This is auto project2</t>
   </si>
   <si>
     <t>Alex Pham</t>
@@ -235,10 +244,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>This is auto test3</t>
-  </si>
-  <si>
-    <t>Lily Nguyen</t>
+    <t>This is auto project3</t>
   </si>
   <si>
     <t>05-10-2027</t>
@@ -259,10 +265,7 @@
     <t>50</t>
   </si>
   <si>
-    <t>This is auto test4</t>
-  </si>
-  <si>
-    <t>Long Tran</t>
+    <t>This is auto project4</t>
   </si>
   <si>
     <t>05-10-2028</t>
@@ -277,10 +280,7 @@
     <t>68</t>
   </si>
   <si>
-    <t>This is auto test5</t>
-  </si>
-  <si>
-    <t>Billy Billy</t>
+    <t>This is auto project5</t>
   </si>
   <si>
     <t>05-10-2029</t>
@@ -298,10 +298,7 @@
     <t>TC06</t>
   </si>
   <si>
-    <t>This is auto test6</t>
-  </si>
-  <si>
-    <t>Tommy VN</t>
+    <t>This is auto project6</t>
   </si>
   <si>
     <t>05-10-2025</t>
@@ -319,10 +316,52 @@
     <t>9</t>
   </si>
   <si>
+    <t>Title task</t>
+  </si>
+  <si>
     <t>Endate</t>
   </si>
   <si>
     <t>Project</t>
+  </si>
+  <si>
+    <t>This is auto task1</t>
+  </si>
+  <si>
+    <t>20-12-2025</t>
+  </si>
+  <si>
+    <t>This is a test task with more than sixty characters to meet the requirement.</t>
+  </si>
+  <si>
+    <t>This is auto task2</t>
+  </si>
+  <si>
+    <t>20-12-2026</t>
+  </si>
+  <si>
+    <t>This is auto task3</t>
+  </si>
+  <si>
+    <t>01-01-2027</t>
+  </si>
+  <si>
+    <t>This is auto task4</t>
+  </si>
+  <si>
+    <t>01-01-2028</t>
+  </si>
+  <si>
+    <t>This is auto task5</t>
+  </si>
+  <si>
+    <t>01-01-2029</t>
+  </si>
+  <si>
+    <t>This is auto task6</t>
+  </si>
+  <si>
+    <t>01-01-2030</t>
   </si>
 </sst>
 </file>
@@ -330,10 +369,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -371,8 +410,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,8 +456,69 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -402,106 +533,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -516,187 +555,193 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,6 +752,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -720,16 +776,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -751,41 +822,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -798,19 +852,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -828,137 +873,138 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1313,31 +1359,31 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="6"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1393,28 +1439,28 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="I2" t="s">
@@ -1425,28 +1471,28 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>29</v>
       </c>
       <c r="I3" t="s">
@@ -1457,28 +1503,28 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>34</v>
       </c>
       <c r="I4" t="s">
@@ -1489,28 +1535,28 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G5" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="I5" t="s">
@@ -1521,28 +1567,28 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G6" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I6" t="s">
@@ -1561,11 +1607,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="12.5619047619048" customWidth="1"/>
-    <col min="2" max="2" width="16.0571428571429" customWidth="1"/>
+    <col min="2" max="2" width="19.8666666666667" customWidth="1"/>
     <col min="3" max="3" width="10.7809523809524" customWidth="1"/>
     <col min="4" max="4" width="10.8380952380952" customWidth="1"/>
     <col min="5" max="5" width="11.0952380952381" customWidth="1"/>
@@ -1574,7 +1620,7 @@
     <col min="8" max="8" width="12.6190476190476" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1605,197 +1651,239 @@
       <c r="J1" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="3" t="s">
+      <c r="K1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="C2" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="D2" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>60</v>
+      </c>
       <c r="F2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="H2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" t="s">
         <v>61</v>
       </c>
-      <c r="I2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" s="9" t="s">
+      <c r="G3" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="I6" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="J6" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="K6" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="9" t="s">
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="H3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s">
-        <v>78</v>
-      </c>
-      <c r="J4" s="9" t="s">
+      <c r="D7" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="9" t="s">
+      <c r="I7" t="s">
         <v>97</v>
       </c>
-      <c r="H7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>99</v>
+      <c r="K7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1807,20 +1895,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="11.6857142857143" customWidth="1"/>
     <col min="2" max="2" width="16.4857142857143" customWidth="1"/>
     <col min="3" max="3" width="10.0666666666667" customWidth="1"/>
+    <col min="4" max="4" width="11.8857142857143" customWidth="1"/>
+    <col min="5" max="5" width="18.6285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>48</v>
@@ -1834,53 +1924,126 @@
       <c r="F1" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+      <c r="B4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
+      <c r="B5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" t="s">
         <v>93</v>
+      </c>
+      <c r="F7" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13035" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12765" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
@@ -369,10 +369,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -397,6 +397,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -404,7 +411,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -418,11 +449,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -433,16 +486,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -456,62 +525,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -524,21 +539,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -561,13 +561,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,85 +651,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,73 +717,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,6 +752,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -769,8 +793,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,26 +829,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -843,160 +852,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12765" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="13035" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
@@ -88,7 +88,7 @@
     <t>annguyen</t>
   </si>
   <si>
-    <t>src/test/resources/testdata/test.jpg</t>
+    <t>src\test\resources\testdata\test.jpg</t>
   </si>
   <si>
     <t>Vietnam</t>
@@ -369,10 +369,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -411,7 +411,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -425,6 +425,84 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -433,79 +511,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -517,28 +526,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -561,187 +561,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -760,6 +760,36 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -799,36 +829,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -855,7 +855,7 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -873,134 +873,134 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1012,6 +1012,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1365,7 +1366,7 @@
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1448,10 +1449,10 @@
       <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="6" t="s">
@@ -1463,7 +1464,7 @@
       <c r="H2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J2" t="s">
@@ -1483,7 +1484,7 @@
       <c r="D3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -1495,7 +1496,7 @@
       <c r="H3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J3" t="s">
@@ -1515,7 +1516,7 @@
       <c r="D4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>32</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -1527,7 +1528,7 @@
       <c r="H4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J4" t="s">
@@ -1547,7 +1548,7 @@
       <c r="D5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>32</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -1559,7 +1560,7 @@
       <c r="H5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J5" t="s">
@@ -1579,7 +1580,7 @@
       <c r="D6" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -1591,7 +1592,7 @@
       <c r="H6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="J6" t="s">
@@ -1668,16 +1669,16 @@
       <c r="C2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>60</v>
       </c>
       <c r="F2" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="11" t="s">
         <v>62</v>
       </c>
       <c r="H2" t="s">
@@ -1686,7 +1687,7 @@
       <c r="I2" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="11" t="s">
         <v>65</v>
       </c>
       <c r="K2" t="s">
@@ -1706,16 +1707,16 @@
       <c r="C3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>70</v>
       </c>
       <c r="F3" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>71</v>
       </c>
       <c r="H3" t="s">
@@ -1724,7 +1725,7 @@
       <c r="I3" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="11" t="s">
         <v>74</v>
       </c>
       <c r="K3" t="s">
@@ -1744,16 +1745,16 @@
       <c r="C4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>77</v>
       </c>
       <c r="F4" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="11" t="s">
         <v>78</v>
       </c>
       <c r="H4" t="s">
@@ -1762,7 +1763,7 @@
       <c r="I4" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
@@ -1782,16 +1783,16 @@
       <c r="C5" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>84</v>
       </c>
       <c r="F5" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="11" t="s">
         <v>85</v>
       </c>
       <c r="H5" t="s">
@@ -1800,7 +1801,7 @@
       <c r="I5" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>86</v>
       </c>
       <c r="K5" t="s">
@@ -1820,16 +1821,16 @@
       <c r="C6" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>89</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="11" t="s">
         <v>90</v>
       </c>
       <c r="H6" t="s">
@@ -1838,7 +1839,7 @@
       <c r="I6" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>91</v>
       </c>
       <c r="K6" t="s">
@@ -1858,16 +1859,16 @@
       <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>95</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>96</v>
       </c>
       <c r="H7" t="s">
@@ -1876,7 +1877,7 @@
       <c r="I7" t="s">
         <v>97</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="11" t="s">
         <v>98</v>
       </c>
       <c r="K7" t="s">
@@ -1933,10 +1934,10 @@
       <c r="B2" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>103</v>
       </c>
       <c r="E2" t="s">
@@ -1953,10 +1954,10 @@
       <c r="B3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E3" t="s">
@@ -1973,10 +1974,10 @@
       <c r="B4" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>77</v>
       </c>
       <c r="E4" t="s">
@@ -1993,10 +1994,10 @@
       <c r="B5" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>84</v>
       </c>
       <c r="E5" t="s">
@@ -2013,10 +2014,10 @@
       <c r="B6" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>89</v>
       </c>
       <c r="E6" t="s">
@@ -2033,10 +2034,10 @@
       <c r="B7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>95</v>
       </c>
       <c r="E7" t="s">

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13035" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="13035" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
@@ -369,10 +369,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -397,14 +397,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -426,6 +426,83 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -442,70 +519,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -525,20 +539,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -561,187 +561,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,6 +764,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -775,6 +799,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -794,21 +827,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -816,24 +834,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -855,7 +855,7 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -873,130 +873,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13035" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="13035" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
     <sheet name="Client" sheetId="1" r:id="rId2"/>
     <sheet name="Project" sheetId="3" r:id="rId3"/>
     <sheet name="Task" sheetId="4" r:id="rId4"/>
+    <sheet name="E2E" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="136">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -362,6 +363,69 @@
   </si>
   <si>
     <t>01-01-2030</t>
+  </si>
+  <si>
+    <t>Username_admin</t>
+  </si>
+  <si>
+    <t>Password_admin</t>
+  </si>
+  <si>
+    <t>Password_client</t>
+  </si>
+  <si>
+    <t>Contact number</t>
+  </si>
+  <si>
+    <t>Username_client</t>
+  </si>
+  <si>
+    <t>Filepath</t>
+  </si>
+  <si>
+    <t>Startdate project</t>
+  </si>
+  <si>
+    <t>Endate project</t>
+  </si>
+  <si>
+    <t>Summary project</t>
+  </si>
+  <si>
+    <t>Startdate task</t>
+  </si>
+  <si>
+    <t>Endate task</t>
+  </si>
+  <si>
+    <t>Summary task</t>
+  </si>
+  <si>
+    <t>Jack</t>
+  </si>
+  <si>
+    <t>Sparrow</t>
+  </si>
+  <si>
+    <t>jacksparrow@test.com</t>
+  </si>
+  <si>
+    <t>jack_sparrow</t>
+  </si>
+  <si>
+    <t>Project run e2e</t>
+  </si>
+  <si>
+    <t>01-02-2025</t>
+  </si>
+  <si>
+    <t>01-02-2026</t>
+  </si>
+  <si>
+    <t>Jack Sparrow</t>
+  </si>
+  <si>
+    <t>Task run e2e</t>
   </si>
 </sst>
 </file>
@@ -369,9 +433,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
@@ -396,6 +460,21 @@
       <charset val="0"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -404,7 +483,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -422,21 +501,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -472,6 +536,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
@@ -480,23 +552,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -519,7 +583,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -533,14 +597,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,193 +619,217 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,11 +852,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -788,17 +882,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -806,8 +896,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -827,17 +917,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -852,18 +931,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -873,34 +961,34 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -909,109 +997,114 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="10" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1366,7 +1459,7 @@
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="13" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1374,17 +1467,17 @@
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1432,10 +1525,10 @@
       <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1449,22 +1542,22 @@
       <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="12" t="s">
         <v>23</v>
       </c>
       <c r="J2" t="s">
@@ -1475,28 +1568,28 @@
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="12" t="s">
         <v>23</v>
       </c>
       <c r="J3" t="s">
@@ -1507,28 +1600,28 @@
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="12" t="s">
         <v>23</v>
       </c>
       <c r="J4" t="s">
@@ -1539,28 +1632,28 @@
       <c r="A5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="10" t="s">
         <v>27</v>
       </c>
       <c r="G5" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="12" t="s">
         <v>23</v>
       </c>
       <c r="J5" t="s">
@@ -1571,28 +1664,28 @@
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="12" t="s">
         <v>23</v>
       </c>
       <c r="J6" t="s">
@@ -1600,6 +1693,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G6" r:id="rId1" display="billy.billy@test.com"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1634,28 +1730,28 @@
       <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="7" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1669,16 +1765,16 @@
       <c r="C2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="16" t="s">
         <v>60</v>
       </c>
       <c r="F2" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="16" t="s">
         <v>62</v>
       </c>
       <c r="H2" t="s">
@@ -1687,7 +1783,7 @@
       <c r="I2" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="16" t="s">
         <v>65</v>
       </c>
       <c r="K2" t="s">
@@ -1704,19 +1800,19 @@
       <c r="B3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="16" t="s">
         <v>70</v>
       </c>
       <c r="F3" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="16" t="s">
         <v>71</v>
       </c>
       <c r="H3" t="s">
@@ -1725,7 +1821,7 @@
       <c r="I3" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="16" t="s">
         <v>74</v>
       </c>
       <c r="K3" t="s">
@@ -1742,19 +1838,19 @@
       <c r="B4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="16" t="s">
         <v>77</v>
       </c>
       <c r="F4" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="16" t="s">
         <v>78</v>
       </c>
       <c r="H4" t="s">
@@ -1763,7 +1859,7 @@
       <c r="I4" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="16" t="s">
         <v>81</v>
       </c>
       <c r="K4" t="s">
@@ -1783,16 +1879,16 @@
       <c r="C5" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="16" t="s">
         <v>84</v>
       </c>
       <c r="F5" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="16" t="s">
         <v>85</v>
       </c>
       <c r="H5" t="s">
@@ -1801,7 +1897,7 @@
       <c r="I5" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="16" t="s">
         <v>86</v>
       </c>
       <c r="K5" t="s">
@@ -1821,16 +1917,16 @@
       <c r="C6" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="16" t="s">
         <v>89</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="16" t="s">
         <v>90</v>
       </c>
       <c r="H6" t="s">
@@ -1839,7 +1935,7 @@
       <c r="I6" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="16" t="s">
         <v>91</v>
       </c>
       <c r="K6" t="s">
@@ -1859,16 +1955,16 @@
       <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="16" t="s">
         <v>95</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="16" t="s">
         <v>96</v>
       </c>
       <c r="H7" t="s">
@@ -1877,7 +1973,7 @@
       <c r="I7" t="s">
         <v>97</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="16" t="s">
         <v>98</v>
       </c>
       <c r="K7" t="s">
@@ -1910,22 +2006,22 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
@@ -1934,10 +2030,10 @@
       <c r="B2" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="16" t="s">
         <v>103</v>
       </c>
       <c r="E2" t="s">
@@ -1954,10 +2050,10 @@
       <c r="B3" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="16" t="s">
         <v>106</v>
       </c>
       <c r="E3" t="s">
@@ -1974,10 +2070,10 @@
       <c r="B4" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="16" t="s">
         <v>77</v>
       </c>
       <c r="E4" t="s">
@@ -1994,10 +2090,10 @@
       <c r="B5" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="16" t="s">
         <v>84</v>
       </c>
       <c r="E5" t="s">
@@ -2014,10 +2110,10 @@
       <c r="B6" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="16" t="s">
         <v>89</v>
       </c>
       <c r="E6" t="s">
@@ -2034,16 +2130,160 @@
       <c r="B7" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="16" t="s">
         <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>93</v>
       </c>
       <c r="F7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="10.5142857142857" customWidth="1"/>
+    <col min="2" max="2" width="15.7428571428571" customWidth="1"/>
+    <col min="3" max="3" width="15.3619047619048" customWidth="1"/>
+    <col min="6" max="6" width="13.9619047619048" customWidth="1"/>
+    <col min="7" max="7" width="14.2857142857143" customWidth="1"/>
+    <col min="10" max="10" width="14.7619047619048" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" t="s">
+        <v>134</v>
+      </c>
+      <c r="P2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>135</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="T2" t="s">
         <v>104</v>
       </c>
     </row>

--- a/src/test/resources/testdata/HRM.xlsx
+++ b/src/test/resources/testdata/HRM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13035" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="13035" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="132">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -197,172 +197,160 @@
     <t>An Nguyen</t>
   </si>
   <si>
+    <t>04-11-2025</t>
+  </si>
+  <si>
+    <t>Run auto test</t>
+  </si>
+  <si>
+    <t>09-09-2026</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Highest</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Image test</t>
+  </si>
+  <si>
+    <t>This is auto project2</t>
+  </si>
+  <si>
+    <t>Alex Pham</t>
+  </si>
+  <si>
+    <t>05-09-2025</t>
+  </si>
+  <si>
+    <t>01-11-2026</t>
+  </si>
+  <si>
+    <t>09-09-2027</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>This is auto project3</t>
+  </si>
+  <si>
+    <t>05-10-2027</t>
+  </si>
+  <si>
+    <t>20-12-2027</t>
+  </si>
+  <si>
+    <t>09-09-2028</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>This is auto project4</t>
+  </si>
+  <si>
+    <t>05-10-2028</t>
+  </si>
+  <si>
+    <t>20-12-2028</t>
+  </si>
+  <si>
+    <t>09-09-2029</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>This is auto project5</t>
+  </si>
+  <si>
+    <t>05-10-2029</t>
+  </si>
+  <si>
+    <t>20-12-2029</t>
+  </si>
+  <si>
+    <t>09-09-2030</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Title task</t>
+  </si>
+  <si>
+    <t>Endate</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>This is auto task1</t>
+  </si>
+  <si>
     <t>01-01-2025</t>
   </si>
   <si>
+    <t>20-12-2025</t>
+  </si>
+  <si>
+    <t>This is a test task with more than sixty characters to meet the requirement.</t>
+  </si>
+  <si>
+    <t>This is auto task2</t>
+  </si>
+  <si>
     <t>01-01-2026</t>
   </si>
   <si>
-    <t>Run auto test</t>
-  </si>
-  <si>
-    <t>09-09-2026</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Highest</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>Image test</t>
-  </si>
-  <si>
-    <t>This is auto project2</t>
-  </si>
-  <si>
-    <t>Alex Pham</t>
-  </si>
-  <si>
-    <t>05-09-2025</t>
-  </si>
-  <si>
-    <t>01-11-2026</t>
-  </si>
-  <si>
-    <t>09-09-2027</t>
-  </si>
-  <si>
-    <t>On Hold</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>This is auto project3</t>
-  </si>
-  <si>
-    <t>05-10-2027</t>
-  </si>
-  <si>
-    <t>20-12-2027</t>
-  </si>
-  <si>
-    <t>09-09-2028</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>This is auto project4</t>
-  </si>
-  <si>
-    <t>05-10-2028</t>
-  </si>
-  <si>
-    <t>20-12-2028</t>
-  </si>
-  <si>
-    <t>09-09-2029</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>This is auto project5</t>
-  </si>
-  <si>
-    <t>05-10-2029</t>
-  </si>
-  <si>
-    <t>20-12-2029</t>
-  </si>
-  <si>
-    <t>09-09-2030</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>20-12-2026</t>
+  </si>
+  <si>
+    <t>This is auto task3</t>
+  </si>
+  <si>
+    <t>01-01-2027</t>
+  </si>
+  <si>
+    <t>This is auto task4</t>
+  </si>
+  <si>
+    <t>01-01-2028</t>
+  </si>
+  <si>
+    <t>This is auto task5</t>
+  </si>
+  <si>
+    <t>01-01-2029</t>
   </si>
   <si>
     <t>TC06</t>
   </si>
   <si>
-    <t>This is auto project6</t>
-  </si>
-  <si>
-    <t>05-10-2025</t>
+    <t>This is auto task6</t>
+  </si>
+  <si>
+    <t>01-01-2030</t>
   </si>
   <si>
     <t>20-12-2030</t>
-  </si>
-  <si>
-    <t>09-09-2031</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Title task</t>
-  </si>
-  <si>
-    <t>Endate</t>
-  </si>
-  <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>This is auto task1</t>
-  </si>
-  <si>
-    <t>20-12-2025</t>
-  </si>
-  <si>
-    <t>This is a test task with more than sixty characters to meet the requirement.</t>
-  </si>
-  <si>
-    <t>This is auto task2</t>
-  </si>
-  <si>
-    <t>20-12-2026</t>
-  </si>
-  <si>
-    <t>This is auto task3</t>
-  </si>
-  <si>
-    <t>01-01-2027</t>
-  </si>
-  <si>
-    <t>This is auto task4</t>
-  </si>
-  <si>
-    <t>01-01-2028</t>
-  </si>
-  <si>
-    <t>This is auto task5</t>
-  </si>
-  <si>
-    <t>01-01-2029</t>
-  </si>
-  <si>
-    <t>This is auto task6</t>
-  </si>
-  <si>
-    <t>01-01-2030</t>
   </si>
   <si>
     <t>Username_admin</t>
@@ -469,7 +457,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -483,14 +471,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -501,14 +489,6 @@
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -528,24 +508,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -559,8 +524,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -568,6 +556,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -589,20 +584,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="39">
     <fill>
@@ -649,12 +637,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -667,169 +817,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,26 +831,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -896,23 +884,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -931,19 +928,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -961,130 +949,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1704,8 +1692,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="12.5619047619048" customWidth="1"/>
     <col min="2" max="2" width="19.8666666666667" customWidth="1"/>
@@ -1769,25 +1757,25 @@
         <v>59</v>
       </c>
       <c r="E2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
         <v>60</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="H2" t="s">
         <v>62</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>63</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="K2" t="s">
         <v>65</v>
-      </c>
-      <c r="K2" t="s">
-        <v>66</v>
       </c>
       <c r="L2" t="s">
         <v>23</v>
@@ -1798,34 +1786,34 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="F3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="16" t="s">
+      <c r="H3" t="s">
         <v>71</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>72</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="16" t="s">
-        <v>74</v>
-      </c>
       <c r="K3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L3" t="s">
         <v>23</v>
@@ -1836,34 +1824,34 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="E4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" t="s">
         <v>78</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>79</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="16" t="s">
-        <v>81</v>
-      </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -1874,34 +1862,34 @@
         <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
         <v>58</v>
       </c>
       <c r="D5" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="H5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>86</v>
-      </c>
       <c r="K5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L5" t="s">
         <v>23</v>
@@ -1912,74 +1900,36 @@
         <v>41</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H6" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>91</v>
-      </c>
       <c r="K6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="H7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="K7" t="s">
-        <v>66</v>
-      </c>
-      <c r="L7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2007,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>48</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>50</v>
@@ -2028,19 +1978,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2048,19 +1998,19 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2068,19 +2018,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2088,19 +2038,19 @@
         <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2108,39 +2058,39 @@
         <v>41</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2168,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>10</v>
@@ -2180,10 +2130,10 @@
         <v>11</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>13</v>
@@ -2192,37 +2142,37 @@
         <v>14</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>46</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="O1" s="5" t="s">
         <v>47</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="S1" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -2236,10 +2186,10 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F2" s="16" t="s">
         <v>5</v>
@@ -2251,40 +2201,40 @@
         <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K2" t="s">
         <v>23</v>
       </c>
       <c r="L2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" t="s">
+        <v>130</v>
+      </c>
+      <c r="P2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="s">
         <v>131</v>
       </c>
-      <c r="M2" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="O2" t="s">
-        <v>134</v>
-      </c>
-      <c r="P2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>135</v>
-      </c>
       <c r="R2" s="16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="S2" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="T2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
